--- a/invest/基金.xlsx
+++ b/invest/基金.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="513500标普500" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
   <si>
     <t>日期</t>
   </si>
@@ -1028,7 +1028,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:L1002"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1"/>
@@ -1072,11 +1072,11 @@
         <v>2.198</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" ref="E2:E65" si="0">IF(B2="买入",C2/D2,IF(B2="卖出",-C2/D2,0))</f>
+        <f>IF(B2="买入",C2/D2,IF(B2="卖出",-C2/D2,0))</f>
         <v>2200</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:F65" si="1">IF(B2="买入",-C2,IF(B2="卖出",C2,0))</f>
+        <f>IF(B2="买入",-C2,IF(B2="卖出",C2,0))</f>
         <v>-4835.6</v>
       </c>
     </row>
@@ -1094,11 +1094,11 @@
         <v>2.283</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B3="买入",C3/D3,IF(B3="卖出",-C3/D3,0))</f>
         <v>2100</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B3="买入",-C3,IF(B3="卖出",C3,0))</f>
         <v>-4794.3</v>
       </c>
     </row>
@@ -1116,11 +1116,11 @@
         <v>2.315</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B4="买入",C4/D4,IF(B4="卖出",-C4/D4,0))</f>
         <v>2100</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B4="买入",-C4,IF(B4="卖出",C4,0))</f>
         <v>-4861.5</v>
       </c>
     </row>
@@ -1138,18 +1138,18 @@
         <v>2.287</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B5="买入",C5/D5,IF(B5="卖出",-C5/D5,0))</f>
         <v>2100</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B5="买入",-C5,IF(B5="卖出",C5,0))</f>
         <v>-4802.7</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L5" s="1">
-        <f>SUMIFS(C2:C23,B2:B23,"买入")</f>
+        <f>SUMIFS(C2:C24,B2:B24,"买入")</f>
         <v>97870.7</v>
       </c>
     </row>
@@ -1167,19 +1167,19 @@
         <v>2.338</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B6="买入",C6/D6,IF(B6="卖出",-C6/D6,0))</f>
         <v>2100</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B6="买入",-C6,IF(B6="卖出",C6,0))</f>
         <v>-4909.8</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L6" s="1">
-        <f>SUMIFS(C2:C23,B2:B23,"卖出")</f>
-        <v>107996.5</v>
+        <f>SUMIFS(C2:C24,B2:B24,"卖出")</f>
+        <v>109404.5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:12">
@@ -1196,11 +1196,11 @@
         <v>2.469</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B7="买入",C7/D7,IF(B7="卖出",-C7/D7,0))</f>
         <v>2000</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B7="买入",-C7,IF(B7="卖出",C7,0))</f>
         <v>-4938</v>
       </c>
     </row>
@@ -1218,11 +1218,11 @@
         <v>2.428</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B8="买入",C8/D8,IF(B8="卖出",-C8/D8,0))</f>
         <v>2000</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B8="买入",-C8,IF(B8="卖出",C8,0))</f>
         <v>-4856</v>
       </c>
     </row>
@@ -1240,11 +1240,11 @@
         <v>2.459</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B9="买入",C9/D9,IF(B9="卖出",-C9/D9,0))</f>
         <v>2000</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B9="买入",-C9,IF(B9="卖出",C9,0))</f>
         <v>-4918</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="L9" s="1">
         <f>L8+L6-L5</f>
-        <v>10125.8</v>
+        <v>11533.8</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:12">
@@ -1269,11 +1269,11 @@
         <v>2.431</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B10="买入",C10/D10,IF(B10="卖出",-C10/D10,0))</f>
         <v>2000</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B10="买入",-C10,IF(B10="卖出",C10,0))</f>
         <v>-4862</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="L10" s="5">
         <f>IFERROR(L9/L5,0)</f>
-        <v>0.103460994965807</v>
+        <v>0.117847323049697</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:12">
@@ -1298,11 +1298,11 @@
         <v>2.432</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B11="买入",C11/D11,IF(B11="卖出",-C11/D11,0))</f>
         <v>2000</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B11="买入",-C11,IF(B11="卖出",C11,0))</f>
         <v>-4864</v>
       </c>
     </row>
@@ -1320,11 +1320,11 @@
         <v>2.457</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B12="买入",C12/D12,IF(B12="卖出",-C12/D12,0))</f>
         <v>2000</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B12="买入",-C12,IF(B12="卖出",C12,0))</f>
         <v>-4914</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="L12" s="1">
         <f ca="1">TODAY()-A2</f>
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:12">
@@ -1349,19 +1349,19 @@
         <v>2.424</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B13="买入",C13/D13,IF(B13="卖出",-C13/D13,0))</f>
         <v>2000</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B13="买入",-C13,IF(B13="卖出",C13,0))</f>
         <v>-4848</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="L13" s="5">
-        <f ca="1">XIRR(F2:F23,A2:A23)</f>
-        <v>0.246099064688374</v>
+        <f ca="1">XIRR(F2:F24,A2:A24)</f>
+        <v>0.280246031626223</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:12">
@@ -1378,19 +1378,19 @@
         <v>2.384</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B14="买入",C14/D14,IF(B14="卖出",-C14/D14,0))</f>
         <v>2000</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B14="买入",-C14,IF(B14="卖出",C14,0))</f>
         <v>-4768</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="L14" s="5">
-        <f>MAX(D2:D22)-D23</f>
-        <v>-0.139</v>
+        <f>MAX(D2:D22)-D24</f>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:12">
@@ -1407,11 +1407,11 @@
         <v>2.376</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B15="买入",C15/D15,IF(B15="卖出",-C15/D15,0))</f>
         <v>2100</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B15="买入",-C15,IF(B15="卖出",C15,0))</f>
         <v>-4989.6</v>
       </c>
     </row>
@@ -1429,11 +1429,11 @@
         <v>2.314</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B16="买入",C16/D16,IF(B16="卖出",-C16/D16,0))</f>
         <v>2100</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B16="买入",-C16,IF(B16="卖出",C16,0))</f>
         <v>-4859.4</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1458,11 +1458,11 @@
         <v>2.171</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B17="买入",C17/D17,IF(B17="卖出",-C17/D17,0))</f>
         <v>2300</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B17="买入",-C17,IF(B17="卖出",C17,0))</f>
         <v>-4993.3</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1487,11 +1487,11 @@
         <v>2.211</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B18="买入",C18/D18,IF(B18="卖出",-C18/D18,0))</f>
         <v>2200</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B18="买入",-C18,IF(B18="卖出",C18,0))</f>
         <v>-4864.2</v>
       </c>
     </row>
@@ -1509,11 +1509,11 @@
         <v>2.36</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B19="买入",C19/D19,IF(B19="卖出",-C19/D19,0))</f>
         <v>2100</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B19="买入",-C19,IF(B19="卖出",C19,0))</f>
         <v>-4956</v>
       </c>
     </row>
@@ -1531,11 +1531,11 @@
         <v>2.451</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B20="买入",C20/D20,IF(B20="卖出",-C20/D20,0))</f>
         <v>-1500</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B20="买入",-C20,IF(B20="卖出",C20,0))</f>
         <v>3676.5</v>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         <v>2.453</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B21="买入",C21/D21,IF(B21="卖出",-C21/D21,0))</f>
         <v>2000</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B21="买入",-C21,IF(B21="卖出",C21,0))</f>
         <v>-4906</v>
       </c>
     </row>
@@ -1575,45 +1575,57 @@
         <v>2.443</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B22="买入",C22/D22,IF(B22="卖出",-C22/D22,0))</f>
         <v>2100</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B22="买入",-C22,IF(B22="卖出",C22,0))</f>
         <v>-5130.3</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:12">
       <c r="A23" s="3">
-        <f ca="1">TODAY()</f>
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="1">
-        <v>104320</v>
+        <v>10580</v>
       </c>
       <c r="D23" s="1">
-        <v>2.608</v>
+        <v>2.645</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="0"/>
-        <v>-40000</v>
+        <f>IF(B23="买入",C23/D23,IF(B23="卖出",-C23/D23,0))</f>
+        <v>-4000</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="1"/>
-        <v>104320</v>
+        <f>IF(B23="买入",-C23,IF(B23="卖出",C23,0))</f>
+        <v>10580</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:12">
+      <c r="A24" s="3">
+        <f ca="1">TODAY()</f>
+        <v>46175</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1">
+        <v>95148</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2.643</v>
+      </c>
       <c r="E24" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="E24:E66" si="0">IF(B24="买入",C24/D24,IF(B24="卖出",-C24/D24,0))</f>
+        <v>-36000</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="F24:F66" si="1">IF(B24="买入",-C24,IF(B24="卖出",C24,0))</f>
+        <v>95148</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:12">
@@ -2028,21 +2040,21 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="5:6">
       <c r="E66" s="1">
-        <f t="shared" ref="E66:E129" si="2">IF(B66="买入",C66/D66,IF(B66="卖出",-C66/D66,0))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F66" s="1">
-        <f t="shared" ref="F66:F129" si="3">IF(B66="买入",-C66,IF(B66="卖出",C66,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="5:6">
       <c r="E67" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E67:E130" si="2">IF(B67="买入",C67/D67,IF(B67="卖出",-C67/D67,0))</f>
         <v>0</v>
       </c>
       <c r="F67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F67:F130" si="3">IF(B67="买入",-C67,IF(B67="卖出",C67,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -2668,21 +2680,21 @@
     </row>
     <row r="130" s="1" customFormat="1" spans="5:6">
       <c r="E130" s="1">
-        <f t="shared" ref="E130:E193" si="4">IF(B130="买入",C130/D130,IF(B130="卖出",-C130/D130,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F130" s="1">
-        <f t="shared" ref="F130:F193" si="5">IF(B130="买入",-C130,IF(B130="卖出",C130,0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="5:6">
       <c r="E131" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E131:E194" si="4">IF(B131="买入",C131/D131,IF(B131="卖出",-C131/D131,0))</f>
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F131:F194" si="5">IF(B131="买入",-C131,IF(B131="卖出",C131,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -3308,21 +3320,21 @@
     </row>
     <row r="194" s="1" customFormat="1" spans="5:6">
       <c r="E194" s="1">
-        <f t="shared" ref="E194:E257" si="6">IF(B194="买入",C194/D194,IF(B194="卖出",-C194/D194,0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F194" s="1">
-        <f t="shared" ref="F194:F257" si="7">IF(B194="买入",-C194,IF(B194="卖出",C194,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" spans="5:6">
       <c r="E195" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E195:E258" si="6">IF(B195="买入",C195/D195,IF(B195="卖出",-C195/D195,0))</f>
         <v>0</v>
       </c>
       <c r="F195" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F195:F258" si="7">IF(B195="买入",-C195,IF(B195="卖出",C195,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -3948,21 +3960,21 @@
     </row>
     <row r="258" s="1" customFormat="1" spans="5:6">
       <c r="E258" s="1">
-        <f t="shared" ref="E258:E321" si="8">IF(B258="买入",C258/D258,IF(B258="卖出",-C258/D258,0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F258" s="1">
-        <f t="shared" ref="F258:F321" si="9">IF(B258="买入",-C258,IF(B258="卖出",C258,0))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="259" s="1" customFormat="1" spans="5:6">
       <c r="E259" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E259:E322" si="8">IF(B259="买入",C259/D259,IF(B259="卖出",-C259/D259,0))</f>
         <v>0</v>
       </c>
       <c r="F259" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F259:F322" si="9">IF(B259="买入",-C259,IF(B259="卖出",C259,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -4588,21 +4600,21 @@
     </row>
     <row r="322" s="1" customFormat="1" spans="5:6">
       <c r="E322" s="1">
-        <f t="shared" ref="E322:E385" si="10">IF(B322="买入",C322/D322,IF(B322="卖出",-C322/D322,0))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F322" s="1">
-        <f t="shared" ref="F322:F385" si="11">IF(B322="买入",-C322,IF(B322="卖出",C322,0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" spans="5:6">
       <c r="E323" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E323:E386" si="10">IF(B323="买入",C323/D323,IF(B323="卖出",-C323/D323,0))</f>
         <v>0</v>
       </c>
       <c r="F323" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="F323:F386" si="11">IF(B323="买入",-C323,IF(B323="卖出",C323,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5228,21 +5240,21 @@
     </row>
     <row r="386" s="1" customFormat="1" spans="5:6">
       <c r="E386" s="1">
-        <f t="shared" ref="E386:E449" si="12">IF(B386="买入",C386/D386,IF(B386="卖出",-C386/D386,0))</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F386" s="1">
-        <f t="shared" ref="F386:F449" si="13">IF(B386="买入",-C386,IF(B386="卖出",C386,0))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="387" s="1" customFormat="1" spans="5:6">
       <c r="E387" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="E387:E450" si="12">IF(B387="买入",C387/D387,IF(B387="卖出",-C387/D387,0))</f>
         <v>0</v>
       </c>
       <c r="F387" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F387:F450" si="13">IF(B387="买入",-C387,IF(B387="卖出",C387,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -5868,21 +5880,21 @@
     </row>
     <row r="450" s="1" customFormat="1" spans="5:6">
       <c r="E450" s="1">
-        <f t="shared" ref="E450:E513" si="14">IF(B450="买入",C450/D450,IF(B450="卖出",-C450/D450,0))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F450" s="1">
-        <f t="shared" ref="F450:F513" si="15">IF(B450="买入",-C450,IF(B450="卖出",C450,0))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="451" s="1" customFormat="1" spans="5:6">
       <c r="E451" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="E451:E514" si="14">IF(B451="买入",C451/D451,IF(B451="卖出",-C451/D451,0))</f>
         <v>0</v>
       </c>
       <c r="F451" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F451:F514" si="15">IF(B451="买入",-C451,IF(B451="卖出",C451,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -6508,21 +6520,21 @@
     </row>
     <row r="514" s="1" customFormat="1" spans="5:6">
       <c r="E514" s="1">
-        <f t="shared" ref="E514:E577" si="16">IF(B514="买入",C514/D514,IF(B514="卖出",-C514/D514,0))</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F514" s="1">
-        <f t="shared" ref="F514:F577" si="17">IF(B514="买入",-C514,IF(B514="卖出",C514,0))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="515" s="1" customFormat="1" spans="5:6">
       <c r="E515" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="E515:E578" si="16">IF(B515="买入",C515/D515,IF(B515="卖出",-C515/D515,0))</f>
         <v>0</v>
       </c>
       <c r="F515" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F515:F578" si="17">IF(B515="买入",-C515,IF(B515="卖出",C515,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -7148,21 +7160,21 @@
     </row>
     <row r="578" s="1" customFormat="1" spans="5:6">
       <c r="E578" s="1">
-        <f t="shared" ref="E578:E641" si="18">IF(B578="买入",C578/D578,IF(B578="卖出",-C578/D578,0))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F578" s="1">
-        <f t="shared" ref="F578:F641" si="19">IF(B578="买入",-C578,IF(B578="卖出",C578,0))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="579" s="1" customFormat="1" spans="5:6">
       <c r="E579" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="E579:E642" si="18">IF(B579="买入",C579/D579,IF(B579="卖出",-C579/D579,0))</f>
         <v>0</v>
       </c>
       <c r="F579" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F579:F642" si="19">IF(B579="买入",-C579,IF(B579="卖出",C579,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -7788,21 +7800,21 @@
     </row>
     <row r="642" s="1" customFormat="1" spans="5:6">
       <c r="E642" s="1">
-        <f t="shared" ref="E642:E705" si="20">IF(B642="买入",C642/D642,IF(B642="卖出",-C642/D642,0))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F642" s="1">
-        <f t="shared" ref="F642:F705" si="21">IF(B642="买入",-C642,IF(B642="卖出",C642,0))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="643" s="1" customFormat="1" spans="5:6">
       <c r="E643" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="E643:E706" si="20">IF(B643="买入",C643/D643,IF(B643="卖出",-C643/D643,0))</f>
         <v>0</v>
       </c>
       <c r="F643" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="F643:F706" si="21">IF(B643="买入",-C643,IF(B643="卖出",C643,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -8428,21 +8440,21 @@
     </row>
     <row r="706" s="1" customFormat="1" spans="5:6">
       <c r="E706" s="1">
-        <f t="shared" ref="E706:E769" si="22">IF(B706="买入",C706/D706,IF(B706="卖出",-C706/D706,0))</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F706" s="1">
-        <f t="shared" ref="F706:F769" si="23">IF(B706="买入",-C706,IF(B706="卖出",C706,0))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="707" s="1" customFormat="1" spans="5:6">
       <c r="E707" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="E707:E770" si="22">IF(B707="买入",C707/D707,IF(B707="卖出",-C707/D707,0))</f>
         <v>0</v>
       </c>
       <c r="F707" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="F707:F770" si="23">IF(B707="买入",-C707,IF(B707="卖出",C707,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -9068,21 +9080,21 @@
     </row>
     <row r="770" s="1" customFormat="1" spans="5:6">
       <c r="E770" s="1">
-        <f t="shared" ref="E770:E833" si="24">IF(B770="买入",C770/D770,IF(B770="卖出",-C770/D770,0))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F770" s="1">
-        <f t="shared" ref="F770:F833" si="25">IF(B770="买入",-C770,IF(B770="卖出",C770,0))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="771" s="1" customFormat="1" spans="5:6">
       <c r="E771" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="E771:E834" si="24">IF(B771="买入",C771/D771,IF(B771="卖出",-C771/D771,0))</f>
         <v>0</v>
       </c>
       <c r="F771" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="F771:F834" si="25">IF(B771="买入",-C771,IF(B771="卖出",C771,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -9708,21 +9720,21 @@
     </row>
     <row r="834" s="1" customFormat="1" spans="5:6">
       <c r="E834" s="1">
-        <f t="shared" ref="E834:E897" si="26">IF(B834="买入",C834/D834,IF(B834="卖出",-C834/D834,0))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F834" s="1">
-        <f t="shared" ref="F834:F897" si="27">IF(B834="买入",-C834,IF(B834="卖出",C834,0))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="835" s="1" customFormat="1" spans="5:6">
       <c r="E835" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="E835:E898" si="26">IF(B835="买入",C835/D835,IF(B835="卖出",-C835/D835,0))</f>
         <v>0</v>
       </c>
       <c r="F835" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F835:F898" si="27">IF(B835="买入",-C835,IF(B835="卖出",C835,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -10348,21 +10360,21 @@
     </row>
     <row r="898" s="1" customFormat="1" spans="5:6">
       <c r="E898" s="1">
-        <f t="shared" ref="E898:E961" si="28">IF(B898="买入",C898/D898,IF(B898="卖出",-C898/D898,0))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F898" s="1">
-        <f t="shared" ref="F898:F961" si="29">IF(B898="买入",-C898,IF(B898="卖出",C898,0))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
     <row r="899" s="1" customFormat="1" spans="5:6">
       <c r="E899" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E899:E962" si="28">IF(B899="买入",C899/D899,IF(B899="卖出",-C899/D899,0))</f>
         <v>0</v>
       </c>
       <c r="F899" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="F899:F962" si="29">IF(B899="买入",-C899,IF(B899="卖出",C899,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -10988,21 +11000,21 @@
     </row>
     <row r="962" s="1" customFormat="1" spans="5:6">
       <c r="E962" s="1">
-        <f t="shared" ref="E962:E1001" si="30">IF(B962="买入",C962/D962,IF(B962="卖出",-C962/D962,0))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F962" s="1">
-        <f t="shared" ref="F962:F1001" si="31">IF(B962="买入",-C962,IF(B962="卖出",C962,0))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
     <row r="963" s="1" customFormat="1" spans="5:6">
       <c r="E963" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="E963:E1002" si="30">IF(B963="买入",C963/D963,IF(B963="卖出",-C963/D963,0))</f>
         <v>0</v>
       </c>
       <c r="F963" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="F963:F1002" si="31">IF(B963="买入",-C963,IF(B963="卖出",C963,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -11386,9 +11398,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1002" s="1" customFormat="1" spans="5:6">
+      <c r="E1002" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="F1002" s="1">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B1:B22 B24:B1048576">
       <formula1>"买入,卖出"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11401,7 +11423,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.5" style="1"/>
@@ -11524,7 +11546,7 @@
         <v>7</v>
       </c>
       <c r="L5" s="1">
-        <f>SUMIFS(C2:C22,B2:B22,"买入")</f>
+        <f>SUMIFS(C2:C23,B2:B23,"买入")</f>
         <v>33434.1</v>
       </c>
     </row>
@@ -11553,7 +11575,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="1">
-        <f>SUMIFS(C2:C22,B2:B22,"卖出")</f>
+        <f>SUMIFS(C2:C23,B2:B23,"卖出")</f>
         <v>40976</v>
       </c>
     </row>
@@ -11593,11 +11615,11 @@
         <v>2.303</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" ref="E8:E64" si="2">IF(B8="买入",C8/D8,IF(B8="卖出",-C8/D8,0))</f>
+        <f>IF(B8="买入",C8/D8,IF(B8="卖出",-C8/D8,0))</f>
         <v>2000</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" ref="F8:F64" si="3">IF(B8="买入",-C8,IF(B8="卖出",C8,0))</f>
+        <f>IF(B8="买入",-C8,IF(B8="卖出",C8,0))</f>
         <v>-4606</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -11622,11 +11644,11 @@
         <v>2.365</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="2"/>
+        <f>IF(B9="买入",C9/D9,IF(B9="卖出",-C9/D9,0))</f>
         <v>1800</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="3"/>
+        <f>IF(B9="买入",-C9,IF(B9="卖出",C9,0))</f>
         <v>-4257</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -11638,47 +11660,38 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:12">
-      <c r="A10" s="3">
+      <c r="A10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="1">
+        <f>IF(B10="买入",C10/D10,IF(B10="卖出",-C10/D10,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <f>IF(B10="买入",-C10,IF(B10="卖出",C10,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:12">
+      <c r="A11" s="3">
         <f ca="1">TODAY()</f>
-        <v>46174</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>46175</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="1">
         <v>38776</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D11" s="4">
         <v>2.62</v>
       </c>
-      <c r="E10" s="1">
-        <f t="shared" ref="E10:E18" si="4">IF(B10="买入",C10/D10,IF(B10="卖出",-C10/D10,0))</f>
+      <c r="E11" s="1">
+        <f t="shared" ref="E11:E19" si="2">IF(B11="买入",C11/D11,IF(B11="卖出",-C11/D11,0))</f>
         <v>-14800</v>
       </c>
-      <c r="F10" s="1">
-        <f t="shared" si="3"/>
+      <c r="F11" s="1">
+        <f t="shared" ref="F11:F65" si="3">IF(B11="买入",-C11,IF(B11="卖出",C11,0))</f>
         <v>38776</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:12">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <f t="shared" ref="F10:F18" si="5">IF(B11="买入",-C11,IF(B11="卖出",C11,0))</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L11" s="1">
-        <f ca="1">TODAY()-A2</f>
-        <v>115</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:12">
@@ -11687,19 +11700,19 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F11:F19" si="4">IF(B12="买入",-C12,IF(B12="卖出",C12,0))</f>
         <v>0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="5">
-        <f ca="1">XIRR(F2:F10,A2:A10)</f>
-        <v>2.67288408970047</v>
+        <v>11</v>
+      </c>
+      <c r="L12" s="1">
+        <f ca="1">TODAY()-A2</f>
+        <v>116</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:12">
@@ -11708,14 +11721,20 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F13" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="5"/>
+      <c r="K13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="5" t="e">
+        <f ca="1">XIRR(F2:F11,A2:A11)</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:12">
       <c r="A14" s="3"/>
@@ -11723,13 +11742,14 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F14" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:12">
       <c r="A15" s="3"/>
@@ -11737,19 +11757,12 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="1">
-        <f>IF(L13&gt;=0.3,20000,IF(L13&gt;=0.2,15000,IF(L13&gt;=0.1,10000,5000)))</f>
-        <v>5000</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:12">
@@ -11758,74 +11771,85 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F16" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="1" t="str">
-        <f>IF(L13&gt;=0.3,"加仓3倍",IF(L13&gt;=0.2,"加仓2倍",IF(L13&gt;=0.1,"加仓1倍",IF(L9&gt;=0.3,"卖利润30%",IF(L9&gt;=0.2,"卖利润20%",IF(L9&gt;=0.1,"卖利润10%","继续定投"))))))</f>
-        <v>卖利润20%</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="L16" s="1">
+        <f>IF(L14&gt;=0.3,20000,IF(L14&gt;=0.2,15000,IF(L14&gt;=0.1,10000,5000)))</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:12">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F17" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="K17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="1" t="str">
+        <f>IF(L14&gt;=0.3,"加仓3倍",IF(L14&gt;=0.2,"加仓2倍",IF(L14&gt;=0.1,"加仓1倍",IF(L9&gt;=0.3,"卖利润30%",IF(L9&gt;=0.2,"卖利润20%",IF(L9&gt;=0.1,"卖利润10%","继续定投"))))))</f>
+        <v>卖利润20%</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:12">
       <c r="A18" s="3"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F18" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:6">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:12">
       <c r="A19" s="3"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:12">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:6">
+    <row r="21" s="1" customFormat="1" spans="1:12">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:6">
+    <row r="22" s="1" customFormat="1" spans="1:12">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" s="1" customFormat="1" spans="1:6">
-      <c r="E23" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:6">
+    <row r="23" s="1" customFormat="1" spans="1:12">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:12">
       <c r="E24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E11:E65" si="5">IF(B24="买入",C24/D24,IF(B24="卖出",-C24/D24,0))</f>
         <v>0</v>
       </c>
       <c r="F24" s="1">
@@ -11833,9 +11857,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:6">
+    <row r="25" s="1" customFormat="1" spans="1:12">
       <c r="E25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F25" s="1">
@@ -11843,9 +11867,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:6">
+    <row r="26" s="1" customFormat="1" spans="1:12">
       <c r="E26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F26" s="1">
@@ -11853,9 +11877,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:6">
+    <row r="27" s="1" customFormat="1" spans="1:12">
       <c r="E27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F27" s="1">
@@ -11863,9 +11887,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:6">
+    <row r="28" s="1" customFormat="1" spans="1:12">
       <c r="E28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F28" s="1">
@@ -11873,9 +11897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:6">
+    <row r="29" s="1" customFormat="1" spans="1:12">
       <c r="E29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F29" s="1">
@@ -11883,9 +11907,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:6">
+    <row r="30" s="1" customFormat="1" spans="1:12">
       <c r="E30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F30" s="1">
@@ -11893,9 +11917,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:6">
+    <row r="31" s="1" customFormat="1" spans="1:12">
       <c r="E31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F31" s="1">
@@ -11903,9 +11927,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:6">
+    <row r="32" s="1" customFormat="1" spans="1:12">
       <c r="E32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F32" s="1">
@@ -11915,7 +11939,7 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="5:6">
       <c r="E33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F33" s="1">
@@ -11925,7 +11949,7 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="5:6">
       <c r="E34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F34" s="1">
@@ -11935,7 +11959,7 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="5:6">
       <c r="E35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F35" s="1">
@@ -11945,7 +11969,7 @@
     </row>
     <row r="36" s="1" customFormat="1" spans="5:6">
       <c r="E36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F36" s="1">
@@ -11955,7 +11979,7 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="5:6">
       <c r="E37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F37" s="1">
@@ -11965,7 +11989,7 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="5:6">
       <c r="E38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F38" s="1">
@@ -11975,7 +11999,7 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="5:6">
       <c r="E39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F39" s="1">
@@ -11985,7 +12009,7 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="5:6">
       <c r="E40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F40" s="1">
@@ -11995,7 +12019,7 @@
     </row>
     <row r="41" s="1" customFormat="1" spans="5:6">
       <c r="E41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F41" s="1">
@@ -12005,7 +12029,7 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="5:6">
       <c r="E42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F42" s="1">
@@ -12015,7 +12039,7 @@
     </row>
     <row r="43" s="1" customFormat="1" spans="5:6">
       <c r="E43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F43" s="1">
@@ -12025,7 +12049,7 @@
     </row>
     <row r="44" s="1" customFormat="1" spans="5:6">
       <c r="E44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F44" s="1">
@@ -12035,7 +12059,7 @@
     </row>
     <row r="45" s="1" customFormat="1" spans="5:6">
       <c r="E45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F45" s="1">
@@ -12045,7 +12069,7 @@
     </row>
     <row r="46" s="1" customFormat="1" spans="5:6">
       <c r="E46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F46" s="1">
@@ -12055,7 +12079,7 @@
     </row>
     <row r="47" s="1" customFormat="1" spans="5:6">
       <c r="E47" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F47" s="1">
@@ -12065,7 +12089,7 @@
     </row>
     <row r="48" s="1" customFormat="1" spans="5:6">
       <c r="E48" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F48" s="1">
@@ -12075,7 +12099,7 @@
     </row>
     <row r="49" s="1" customFormat="1" spans="5:6">
       <c r="E49" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F49" s="1">
@@ -12085,7 +12109,7 @@
     </row>
     <row r="50" s="1" customFormat="1" spans="5:6">
       <c r="E50" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F50" s="1">
@@ -12095,7 +12119,7 @@
     </row>
     <row r="51" s="1" customFormat="1" spans="5:6">
       <c r="E51" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F51" s="1">
@@ -12105,7 +12129,7 @@
     </row>
     <row r="52" s="1" customFormat="1" spans="5:6">
       <c r="E52" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F52" s="1">
@@ -12115,7 +12139,7 @@
     </row>
     <row r="53" s="1" customFormat="1" spans="5:6">
       <c r="E53" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F53" s="1">
@@ -12125,7 +12149,7 @@
     </row>
     <row r="54" s="1" customFormat="1" spans="5:6">
       <c r="E54" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F54" s="1">
@@ -12135,7 +12159,7 @@
     </row>
     <row r="55" s="1" customFormat="1" spans="5:6">
       <c r="E55" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F55" s="1">
@@ -12145,7 +12169,7 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="5:6">
       <c r="E56" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F56" s="1">
@@ -12155,7 +12179,7 @@
     </row>
     <row r="57" s="1" customFormat="1" spans="5:6">
       <c r="E57" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F57" s="1">
@@ -12165,7 +12189,7 @@
     </row>
     <row r="58" s="1" customFormat="1" spans="5:6">
       <c r="E58" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F58" s="1">
@@ -12175,7 +12199,7 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="5:6">
       <c r="E59" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F59" s="1">
@@ -12185,7 +12209,7 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="5:6">
       <c r="E60" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F60" s="1">
@@ -12195,7 +12219,7 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="5:6">
       <c r="E61" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F61" s="1">
@@ -12205,7 +12229,7 @@
     </row>
     <row r="62" s="1" customFormat="1" spans="5:6">
       <c r="E62" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F62" s="1">
@@ -12215,7 +12239,7 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="5:6">
       <c r="E63" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F63" s="1">
@@ -12225,7 +12249,7 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="5:6">
       <c r="E64" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F64" s="1">
@@ -12235,21 +12259,21 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="5:6">
       <c r="E65" s="1">
-        <f t="shared" ref="E65:E128" si="6">IF(B65="买入",C65/D65,IF(B65="卖出",-C65/D65,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F65" s="1">
-        <f t="shared" ref="F65:F128" si="7">IF(B65="买入",-C65,IF(B65="卖出",C65,0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="5:6">
       <c r="E66" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E66:E129" si="6">IF(B66="买入",C66/D66,IF(B66="卖出",-C66/D66,0))</f>
         <v>0</v>
       </c>
       <c r="F66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F66:F129" si="7">IF(B66="买入",-C66,IF(B66="卖出",C66,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -12875,21 +12899,21 @@
     </row>
     <row r="129" s="1" customFormat="1" spans="5:6">
       <c r="E129" s="1">
-        <f t="shared" ref="E129:E192" si="8">IF(B129="买入",C129/D129,IF(B129="卖出",-C129/D129,0))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F129" s="1">
-        <f t="shared" ref="F129:F192" si="9">IF(B129="买入",-C129,IF(B129="卖出",C129,0))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="5:6">
       <c r="E130" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E130:E193" si="8">IF(B130="买入",C130/D130,IF(B130="卖出",-C130/D130,0))</f>
         <v>0</v>
       </c>
       <c r="F130" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F130:F193" si="9">IF(B130="买入",-C130,IF(B130="卖出",C130,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -13515,21 +13539,21 @@
     </row>
     <row r="193" s="1" customFormat="1" spans="5:6">
       <c r="E193" s="1">
-        <f t="shared" ref="E193:E256" si="10">IF(B193="买入",C193/D193,IF(B193="卖出",-C193/D193,0))</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F193" s="1">
-        <f t="shared" ref="F193:F256" si="11">IF(B193="买入",-C193,IF(B193="卖出",C193,0))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" spans="5:6">
       <c r="E194" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E194:E257" si="10">IF(B194="买入",C194/D194,IF(B194="卖出",-C194/D194,0))</f>
         <v>0</v>
       </c>
       <c r="F194" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="F194:F257" si="11">IF(B194="买入",-C194,IF(B194="卖出",C194,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14155,21 +14179,21 @@
     </row>
     <row r="257" s="1" customFormat="1" spans="5:6">
       <c r="E257" s="1">
-        <f t="shared" ref="E257:E320" si="12">IF(B257="买入",C257/D257,IF(B257="卖出",-C257/D257,0))</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F257" s="1">
-        <f t="shared" ref="F257:F320" si="13">IF(B257="买入",-C257,IF(B257="卖出",C257,0))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" s="1" customFormat="1" spans="5:6">
       <c r="E258" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="E258:E321" si="12">IF(B258="买入",C258/D258,IF(B258="卖出",-C258/D258,0))</f>
         <v>0</v>
       </c>
       <c r="F258" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="F258:F321" si="13">IF(B258="买入",-C258,IF(B258="卖出",C258,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -14795,21 +14819,21 @@
     </row>
     <row r="321" s="1" customFormat="1" spans="5:6">
       <c r="E321" s="1">
-        <f t="shared" ref="E321:E384" si="14">IF(B321="买入",C321/D321,IF(B321="卖出",-C321/D321,0))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F321" s="1">
-        <f t="shared" ref="F321:F384" si="15">IF(B321="买入",-C321,IF(B321="卖出",C321,0))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" spans="5:6">
       <c r="E322" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="E322:E385" si="14">IF(B322="买入",C322/D322,IF(B322="卖出",-C322/D322,0))</f>
         <v>0</v>
       </c>
       <c r="F322" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F322:F385" si="15">IF(B322="买入",-C322,IF(B322="卖出",C322,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -15435,21 +15459,21 @@
     </row>
     <row r="385" s="1" customFormat="1" spans="5:6">
       <c r="E385" s="1">
-        <f t="shared" ref="E385:E448" si="16">IF(B385="买入",C385/D385,IF(B385="卖出",-C385/D385,0))</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F385" s="1">
-        <f t="shared" ref="F385:F448" si="17">IF(B385="买入",-C385,IF(B385="卖出",C385,0))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="386" s="1" customFormat="1" spans="5:6">
       <c r="E386" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="E386:E449" si="16">IF(B386="买入",C386/D386,IF(B386="卖出",-C386/D386,0))</f>
         <v>0</v>
       </c>
       <c r="F386" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="F386:F449" si="17">IF(B386="买入",-C386,IF(B386="卖出",C386,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -16075,21 +16099,21 @@
     </row>
     <row r="449" s="1" customFormat="1" spans="5:6">
       <c r="E449" s="1">
-        <f t="shared" ref="E449:E512" si="18">IF(B449="买入",C449/D449,IF(B449="卖出",-C449/D449,0))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F449" s="1">
-        <f t="shared" ref="F449:F512" si="19">IF(B449="买入",-C449,IF(B449="卖出",C449,0))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="450" s="1" customFormat="1" spans="5:6">
       <c r="E450" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="E450:E513" si="18">IF(B450="买入",C450/D450,IF(B450="卖出",-C450/D450,0))</f>
         <v>0</v>
       </c>
       <c r="F450" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F450:F513" si="19">IF(B450="买入",-C450,IF(B450="卖出",C450,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -16715,21 +16739,21 @@
     </row>
     <row r="513" s="1" customFormat="1" spans="5:6">
       <c r="E513" s="1">
-        <f t="shared" ref="E513:E576" si="20">IF(B513="买入",C513/D513,IF(B513="卖出",-C513/D513,0))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F513" s="1">
-        <f t="shared" ref="F513:F576" si="21">IF(B513="买入",-C513,IF(B513="卖出",C513,0))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="514" s="1" customFormat="1" spans="5:6">
       <c r="E514" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="E514:E577" si="20">IF(B514="买入",C514/D514,IF(B514="卖出",-C514/D514,0))</f>
         <v>0</v>
       </c>
       <c r="F514" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="F514:F577" si="21">IF(B514="买入",-C514,IF(B514="卖出",C514,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -17355,21 +17379,21 @@
     </row>
     <row r="577" s="1" customFormat="1" spans="5:6">
       <c r="E577" s="1">
-        <f t="shared" ref="E577:E640" si="22">IF(B577="买入",C577/D577,IF(B577="卖出",-C577/D577,0))</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F577" s="1">
-        <f t="shared" ref="F577:F640" si="23">IF(B577="买入",-C577,IF(B577="卖出",C577,0))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="578" s="1" customFormat="1" spans="5:6">
       <c r="E578" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="E578:E641" si="22">IF(B578="买入",C578/D578,IF(B578="卖出",-C578/D578,0))</f>
         <v>0</v>
       </c>
       <c r="F578" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="F578:F641" si="23">IF(B578="买入",-C578,IF(B578="卖出",C578,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -17995,21 +18019,21 @@
     </row>
     <row r="641" s="1" customFormat="1" spans="5:6">
       <c r="E641" s="1">
-        <f t="shared" ref="E641:E704" si="24">IF(B641="买入",C641/D641,IF(B641="卖出",-C641/D641,0))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F641" s="1">
-        <f t="shared" ref="F641:F704" si="25">IF(B641="买入",-C641,IF(B641="卖出",C641,0))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="642" s="1" customFormat="1" spans="5:6">
       <c r="E642" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="E642:E705" si="24">IF(B642="买入",C642/D642,IF(B642="卖出",-C642/D642,0))</f>
         <v>0</v>
       </c>
       <c r="F642" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="F642:F705" si="25">IF(B642="买入",-C642,IF(B642="卖出",C642,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -18635,21 +18659,21 @@
     </row>
     <row r="705" s="1" customFormat="1" spans="5:6">
       <c r="E705" s="1">
-        <f t="shared" ref="E705:E768" si="26">IF(B705="买入",C705/D705,IF(B705="卖出",-C705/D705,0))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F705" s="1">
-        <f t="shared" ref="F705:F768" si="27">IF(B705="买入",-C705,IF(B705="卖出",C705,0))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
     <row r="706" s="1" customFormat="1" spans="5:6">
       <c r="E706" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="E706:E769" si="26">IF(B706="买入",C706/D706,IF(B706="卖出",-C706/D706,0))</f>
         <v>0</v>
       </c>
       <c r="F706" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F706:F769" si="27">IF(B706="买入",-C706,IF(B706="卖出",C706,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -19275,21 +19299,21 @@
     </row>
     <row r="769" s="1" customFormat="1" spans="5:6">
       <c r="E769" s="1">
-        <f t="shared" ref="E769:E832" si="28">IF(B769="买入",C769/D769,IF(B769="卖出",-C769/D769,0))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F769" s="1">
-        <f t="shared" ref="F769:F832" si="29">IF(B769="买入",-C769,IF(B769="卖出",C769,0))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
     <row r="770" s="1" customFormat="1" spans="5:6">
       <c r="E770" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E770:E833" si="28">IF(B770="买入",C770/D770,IF(B770="卖出",-C770/D770,0))</f>
         <v>0</v>
       </c>
       <c r="F770" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="F770:F833" si="29">IF(B770="买入",-C770,IF(B770="卖出",C770,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -19915,21 +19939,21 @@
     </row>
     <row r="833" s="1" customFormat="1" spans="5:6">
       <c r="E833" s="1">
-        <f t="shared" ref="E833:E896" si="30">IF(B833="买入",C833/D833,IF(B833="卖出",-C833/D833,0))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F833" s="1">
-        <f t="shared" ref="F833:F896" si="31">IF(B833="买入",-C833,IF(B833="卖出",C833,0))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
     <row r="834" s="1" customFormat="1" spans="5:6">
       <c r="E834" s="1">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="E834:E897" si="30">IF(B834="买入",C834/D834,IF(B834="卖出",-C834/D834,0))</f>
         <v>0</v>
       </c>
       <c r="F834" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="F834:F897" si="31">IF(B834="买入",-C834,IF(B834="卖出",C834,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -20555,21 +20579,21 @@
     </row>
     <row r="897" s="1" customFormat="1" spans="5:6">
       <c r="E897" s="1">
-        <f t="shared" ref="E897:E960" si="32">IF(B897="买入",C897/D897,IF(B897="卖出",-C897/D897,0))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F897" s="1">
-        <f t="shared" ref="F897:F960" si="33">IF(B897="买入",-C897,IF(B897="卖出",C897,0))</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="898" s="1" customFormat="1" spans="5:6">
       <c r="E898" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="E898:E961" si="32">IF(B898="买入",C898/D898,IF(B898="卖出",-C898/D898,0))</f>
         <v>0</v>
       </c>
       <c r="F898" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="F898:F961" si="33">IF(B898="买入",-C898,IF(B898="卖出",C898,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -21195,21 +21219,21 @@
     </row>
     <row r="961" s="1" customFormat="1" spans="5:6">
       <c r="E961" s="1">
-        <f t="shared" ref="E961:E1000" si="34">IF(B961="买入",C961/D961,IF(B961="卖出",-C961/D961,0))</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F961" s="1">
-        <f t="shared" ref="F961:F1000" si="35">IF(B961="买入",-C961,IF(B961="卖出",C961,0))</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
     <row r="962" s="1" customFormat="1" spans="5:6">
       <c r="E962" s="1">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="E962:E1001" si="34">IF(B962="买入",C962/D962,IF(B962="卖出",-C962/D962,0))</f>
         <v>0</v>
       </c>
       <c r="F962" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="F962:F1001" si="35">IF(B962="买入",-C962,IF(B962="卖出",C962,0))</f>
         <v>0</v>
       </c>
     </row>
@@ -21593,9 +21617,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1001" s="1" customFormat="1" spans="5:6">
+      <c r="E1001" s="1">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="F1001" s="1">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10 B1:B9 B11:B1048576">
       <formula1>"买入,卖出"</formula1>
     </dataValidation>
   </dataValidations>
